--- a/survey_templates/045_financial_service_experience_report_form--survey_templates.xlsx
+++ b/survey_templates/045_financial_service_experience_report_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': 'Insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'financial_advisor'}</t>
+          <t>financial_advisor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': 'Financial Advisor'}</t>
+          <t>Financial Advisor</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_'friendly'}</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': 'Friendly'}</t>
+          <t>Friendly</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_'polite'}</t>
+          <t>polite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': 'Polite'}</t>
+          <t>Polite</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'label':_'not_polite'}</t>
+          <t>not_polite</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'label': 'Not Polite'}</t>
+          <t>Not Polite</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'less_than_1_minute'}</t>
+          <t>less_than_1_minute</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'Less than 1 minute'}</t>
+          <t>Less than 1 minute</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'1-2_minutes'}</t>
+          <t>1-2_minutes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': '1-2 minutes'}</t>
+          <t>1-2 minutes</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'2-5_minutes'}</t>
+          <t>2-5_minutes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': '2-5 minutes'}</t>
+          <t>2-5 minutes</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'label':_'multiple_times'}</t>
+          <t>multiple_times</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'label': 'Multiple Times'}</t>
+          <t>Multiple Times</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_22.1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 22.1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22.2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22.2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_22.3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 22.3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
